--- a/artfynd/A 63893-2021 artfynd.xlsx
+++ b/artfynd/A 63893-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 63893-2021 artfynd.xlsx
+++ b/artfynd/A 63893-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>104947336</v>
+        <v>104947066</v>
       </c>
       <c r="B2" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>430150.3658131312</v>
+        <v>430026</v>
       </c>
       <c r="R2" t="n">
-        <v>6672898.629147403</v>
+        <v>6672821</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,11 +756,6 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
-      </c>
-      <c r="AO2" t="inlineStr">
-        <is>
-          <t>brandstubbe</t>
-        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -792,37 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>104947463</v>
+        <v>104947067</v>
       </c>
       <c r="B3" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -832,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>430045.0228945751</v>
+        <v>430146</v>
       </c>
       <c r="R3" t="n">
-        <v>6672836.459269649</v>
+        <v>6672886</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,21 +840,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -888,11 +853,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>silverved av tall</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -909,15 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>104947067</v>
+        <v>104947238</v>
       </c>
       <c r="B4" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -925,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -949,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>430146.1337867442</v>
+        <v>430106</v>
       </c>
       <c r="R4" t="n">
-        <v>6672885.774300674</v>
+        <v>6672884</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -982,21 +937,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1005,6 +950,11 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1021,15 +971,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>104947066</v>
+        <v>104947463</v>
       </c>
       <c r="B5" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1037,21 +982,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1061,10 +1006,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>430026.2862121395</v>
+        <v>430045</v>
       </c>
       <c r="R5" t="n">
-        <v>6672820.896251108</v>
+        <v>6672836</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,21 +1039,11 @@
           <t>2022-05-17</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-06-29</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1117,6 +1052,11 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1130,6 +1070,414 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>104947464</v>
+      </c>
+      <c r="B6" t="n">
+        <v>79946</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>6453</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Vedskivlav</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Hertelidea botryosa</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>430108</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6672883</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO6" t="inlineStr">
+        <is>
+          <t>silverved av tall</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>104947335</v>
+      </c>
+      <c r="B7" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>430106</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6672884</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO7" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>104947336</v>
+      </c>
+      <c r="B8" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>430150</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6672898</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO8" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>104947337</v>
+      </c>
+      <c r="B9" t="n">
+        <v>79085</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Mellan Busjön, Naren, Bredsjön och Storsjön i Hagfors kommun, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>430295</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6672954</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Hagfors</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ekshärad</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-05-17</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-06-29</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AO9" t="inlineStr">
+        <is>
+          <t>brandstubbe</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Sebastian Kirppu</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63893-2021 artfynd.xlsx
+++ b/artfynd/A 63893-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947066</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947067</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -968,6 +983,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947238</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1070,6 +1090,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947463</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1172,6 +1197,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947464</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1274,6 +1304,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947335</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1376,6 +1411,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947336</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1478,8 +1518,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/104947337</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>